--- a/check_sktimex/Time series models statistics.xlsx
+++ b/check_sktimex/Time series models statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects.github\python_projects\check_sktimex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7F593D-9E16-44A1-ACDF-111964B420A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9870418C-6595-41B8-9BA2-ED5C84CDBF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" xr2:uid="{BEE0EC04-D849-455D-B7C5-3E9BA1007C5C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{BEE0EC04-D849-455D-B7C5-3E9BA1007C5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863793BE-DDDC-45A0-A460-91E4104F57E7}">
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.7109375" customWidth="1"/>
@@ -1895,6 +1895,32 @@
         <v>31</v>
       </c>
     </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C116">
+        <f>SUM(C2:C115)</f>
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <f>SUM(D2:D115)</f>
+        <v>9</v>
+      </c>
+      <c r="E116">
+        <f>SUM(E2:E115)</f>
+        <v>6</v>
+      </c>
+      <c r="F116">
+        <f>SUM(F2:F115)</f>
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <f>SUM(G2:G115)</f>
+        <v>11</v>
+      </c>
+      <c r="H116">
+        <f>SUM(H2:H115)</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
